--- a/ig/main/ValueSet-jdv-deficience-physique-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-deficience-physique-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260716085852</t>
+    <t>20260916095455</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:58:52+01:00</t>
+    <t>2026-09-16T09:54:55+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -107,6 +107,18 @@
     <t>Aphasie, autre et sans précision</t>
   </si>
   <si>
+    <t>R39.8</t>
+  </si>
+  <si>
+    <t>Symptômes et signes relatifs à l'appareil urinaire, autres et non précisés</t>
+  </si>
+  <si>
+    <t>R19.8</t>
+  </si>
+  <si>
+    <t>Autres symptômes et signes précisés relatifs à l'appareil digestif et à l'abdomen</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -138,18 +150,6 @@
   </si>
   <si>
     <t>Trouble de la déglutition</t>
-  </si>
-  <si>
-    <t>MED-333</t>
-  </si>
-  <si>
-    <t>Trouble de l'élimination urinaire</t>
-  </si>
-  <si>
-    <t>MED-334</t>
-  </si>
-  <si>
-    <t>Trouble de l'élimination fécale</t>
   </si>
   <si>
     <t>MED-335</t>
@@ -437,7 +437,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -465,15 +465,31 @@
         <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -483,7 +499,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -500,73 +516,57 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s" s="2">
         <v>47</v>
       </c>
     </row>
@@ -610,15 +610,15 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>52</v>

--- a/ig/main/ValueSet-jdv-deficience-physique-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-deficience-physique-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260916095455</t>
+    <t>20260928134052</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T09:54:55+01:00</t>
+    <t>2026-09-28T13:40:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
